--- a/excel_files/公司人員名單.xlsx
+++ b/excel_files/公司人員名單.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\StephenData\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55F376A-779E-4045-B716-AC3A688C9C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369211C0-5674-4137-9EEF-770717375597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>沈世如</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,30 +194,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>工讀生</t>
-  </si>
-  <si>
-    <t>CE080</t>
-  </si>
-  <si>
-    <t>CE082</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工讀生</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>沈子維</t>
   </si>
   <si>
-    <t>沈子桓</t>
-  </si>
-  <si>
     <t>何忠達</t>
-  </si>
-  <si>
-    <t>簡瑞廷</t>
   </si>
   <si>
     <t>陳庭紘</t>
@@ -320,7 +300,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -526,6 +506,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -533,7 +539,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -594,12 +600,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -629,6 +629,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -935,7 +944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -955,14 +964,14 @@
         <v>17</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5">
@@ -979,7 +988,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A3" s="23"/>
+      <c r="A3" s="21"/>
       <c r="B3" s="3">
         <v>2</v>
       </c>
@@ -994,7 +1003,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A4" s="24"/>
+      <c r="A4" s="22"/>
       <c r="B4" s="3">
         <v>3</v>
       </c>
@@ -1009,7 +1018,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A5" s="25"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="7">
         <v>4</v>
       </c>
@@ -1024,7 +1033,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="24" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="5">
@@ -1041,7 +1050,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A7" s="27"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="3">
         <v>6</v>
       </c>
@@ -1056,7 +1065,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A8" s="28"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="7">
         <v>7</v>
       </c>
@@ -1071,7 +1080,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="27" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="5">
@@ -1088,7 +1097,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A10" s="30"/>
+      <c r="A10" s="28"/>
       <c r="B10" s="3">
         <v>9</v>
       </c>
@@ -1103,7 +1112,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A11" s="30"/>
+      <c r="A11" s="28"/>
       <c r="B11" s="3">
         <v>10</v>
       </c>
@@ -1111,42 +1120,42 @@
         <v>25</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A12" s="30"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="3">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:5" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A13" s="31"/>
-      <c r="B13" s="7">
+      <c r="A13" s="28"/>
+      <c r="B13" s="30">
         <v>12</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="21" t="s">
+      <c r="C13" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="32" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="27" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="5">
@@ -1163,7 +1172,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A15" s="30"/>
+      <c r="A15" s="28"/>
       <c r="B15" s="3">
         <v>14</v>
       </c>
@@ -1178,73 +1187,35 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A16" s="30"/>
-      <c r="B16" s="3"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="3">
+        <v>15</v>
+      </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A17" s="31"/>
+      <c r="A17" s="29"/>
       <c r="B17" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" s="12"/>
     </row>
-    <row r="18" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A18" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="5">
-        <v>16</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A19" s="30"/>
-      <c r="B19" s="3">
-        <v>17</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A20" s="31"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="12"/>
-    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A18:A20"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A9:A13"/>
   </mergeCells>

--- a/excel_files/公司人員名單.xlsx
+++ b/excel_files/公司人員名單.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\StephenData\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369211C0-5674-4137-9EEF-770717375597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14FB4F9-69BD-4E1E-815E-049992D62BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -600,6 +600,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -629,15 +638,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -971,7 +971,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="23" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5">
@@ -988,7 +988,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A3" s="21"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="3">
         <v>2</v>
       </c>
@@ -1003,7 +1003,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A4" s="22"/>
+      <c r="A4" s="25"/>
       <c r="B4" s="3">
         <v>3</v>
       </c>
@@ -1018,7 +1018,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A5" s="23"/>
+      <c r="A5" s="26"/>
       <c r="B5" s="7">
         <v>4</v>
       </c>
@@ -1033,7 +1033,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="27" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="5">
@@ -1050,7 +1050,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A7" s="25"/>
+      <c r="A7" s="28"/>
       <c r="B7" s="3">
         <v>6</v>
       </c>
@@ -1065,7 +1065,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A8" s="26"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="7">
         <v>7</v>
       </c>
@@ -1080,7 +1080,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="30" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="5">
@@ -1097,7 +1097,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A10" s="28"/>
+      <c r="A10" s="31"/>
       <c r="B10" s="3">
         <v>9</v>
       </c>
@@ -1112,7 +1112,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A11" s="28"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="3">
         <v>10</v>
       </c>
@@ -1127,7 +1127,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A12" s="28"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="3">
         <v>11</v>
       </c>
@@ -1140,22 +1140,22 @@
       <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:5" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A13" s="28"/>
-      <c r="B13" s="30">
+      <c r="A13" s="31"/>
+      <c r="B13" s="20">
         <v>12</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="22" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="30" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="5">
@@ -1172,7 +1172,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A15" s="28"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="3">
         <v>14</v>
       </c>
@@ -1187,7 +1187,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="23.1" customHeight="1">
-      <c r="A16" s="28"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="3">
         <v>15</v>
       </c>
@@ -1200,7 +1200,7 @@
       <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A17" s="29"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="7">
         <v>16</v>
       </c>
